--- a/artfynd/A 59265-2024 artfynd.xlsx
+++ b/artfynd/A 59265-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>89261913</v>
       </c>
       <c r="B2" t="n">
-        <v>101323</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>291117.576859138</v>
+        <v>291118</v>
       </c>
       <c r="R2" t="n">
-        <v>6520489.479548533</v>
+        <v>6520489</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1999-09-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1999-09-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>89261905</v>
       </c>
       <c r="B3" t="n">
-        <v>95710</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97646</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>291117.576859138</v>
+        <v>291118</v>
       </c>
       <c r="R3" t="n">
-        <v>6520489.479548533</v>
+        <v>6520489</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -874,19 +854,9 @@
           <t>1999-09-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1999-09-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 59265-2024 artfynd.xlsx
+++ b/artfynd/A 59265-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>89261913</v>
       </c>
       <c r="B2" t="n">
-        <v>103641</v>
+        <v>103652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>89261905</v>
       </c>
       <c r="B3" t="n">
-        <v>97646</v>
+        <v>97652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59265-2024 artfynd.xlsx
+++ b/artfynd/A 59265-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>89261913</v>
       </c>
       <c r="B2" t="n">
-        <v>103652</v>
+        <v>103660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>89261905</v>
       </c>
       <c r="B3" t="n">
-        <v>97652</v>
+        <v>97658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59265-2024 artfynd.xlsx
+++ b/artfynd/A 59265-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>89261913</v>
       </c>
       <c r="B2" t="n">
-        <v>103660</v>
+        <v>103672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>89261905</v>
       </c>
       <c r="B3" t="n">
-        <v>97658</v>
+        <v>97660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59265-2024 artfynd.xlsx
+++ b/artfynd/A 59265-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>89261913</v>
       </c>
       <c r="B2" t="n">
-        <v>103672</v>
+        <v>103680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59265-2024 artfynd.xlsx
+++ b/artfynd/A 59265-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>89261913</v>
       </c>
       <c r="B2" t="n">
-        <v>103680</v>
+        <v>103682</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>89261905</v>
       </c>
       <c r="B3" t="n">
-        <v>97660</v>
+        <v>97661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59265-2024 artfynd.xlsx
+++ b/artfynd/A 59265-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>89261913</v>
       </c>
       <c r="B2" t="n">
-        <v>103682</v>
+        <v>103709</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>89261905</v>
       </c>
       <c r="B3" t="n">
-        <v>97661</v>
+        <v>97688</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59265-2024 artfynd.xlsx
+++ b/artfynd/A 59265-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>89261913</v>
       </c>
       <c r="B2" t="n">
-        <v>103709</v>
+        <v>103715</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>89261905</v>
       </c>
       <c r="B3" t="n">
-        <v>97688</v>
+        <v>97694</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59265-2024 artfynd.xlsx
+++ b/artfynd/A 59265-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>89261913</v>
       </c>
       <c r="B2" t="n">
-        <v>103715</v>
+        <v>103722</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>89261905</v>
       </c>
       <c r="B3" t="n">
-        <v>97694</v>
+        <v>97701</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59265-2024 artfynd.xlsx
+++ b/artfynd/A 59265-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>89261913</v>
       </c>
       <c r="B2" t="n">
-        <v>103722</v>
+        <v>103726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>89261905</v>
       </c>
       <c r="B3" t="n">
-        <v>97701</v>
+        <v>97705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59265-2024 artfynd.xlsx
+++ b/artfynd/A 59265-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>89261913</v>
       </c>
       <c r="B2" t="n">
-        <v>103726</v>
+        <v>103733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>89261905</v>
       </c>
       <c r="B3" t="n">
-        <v>97705</v>
+        <v>97712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59265-2024 artfynd.xlsx
+++ b/artfynd/A 59265-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>89261913</v>
       </c>
       <c r="B2" t="n">
-        <v>103736</v>
+        <v>103741</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>89261905</v>
       </c>
       <c r="B3" t="n">
-        <v>97715</v>
+        <v>97720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59265-2024 artfynd.xlsx
+++ b/artfynd/A 59265-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89261913</v>
+        <v>105271470</v>
       </c>
       <c r="B2" t="n">
-        <v>103741</v>
+        <v>58238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222395</v>
+        <v>103012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>200 m N om jaktstuga, Mungseröd, mellan skogsbilväg (V om) och berg, Boh</t>
+          <t>Mungseröd Vindpark, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>291118</v>
+        <v>290958</v>
       </c>
       <c r="R2" t="n">
-        <v>6520489</v>
+        <v>6520364</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1999-09-03</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1999-09-03</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Bohusläns flora - 2011. Dvärghäxört angiven i Fries (St. Nn)</t>
+          <t>JPN0009 (Calluna AB) häckfågelinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,35 +770,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Bäckravin, sumpskog, bäck</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Evastina Blomgren</t>
+          <t>Josefina Pehrson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kjell Emanuelsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Bohusläns Flora 2011</t>
-        </is>
-      </c>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89261905</v>
+        <v>105271445</v>
       </c>
       <c r="B3" t="n">
-        <v>97720</v>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,37 +797,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220250</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>200 m N om jaktstuga, Mungseröd, mellan skogsbilväg (V om) och berg, Boh</t>
+          <t>Mungseröd Vindpark, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>291118</v>
+        <v>291057</v>
       </c>
       <c r="R3" t="n">
-        <v>6520489</v>
+        <v>6520402</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,17 +860,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1999-09-03</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1999-09-03</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Bohusläns flora - 2011.</t>
+          <t>JPN0009 (Calluna AB) häckfågelinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,62 +881,48 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Bäckravin, sumpskog, bäck</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Evastina Blomgren</t>
+          <t>Josefina Pehrson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kjell Emanuelsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Bohusläns Flora 2011</t>
-        </is>
-      </c>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105271470</v>
+        <v>105271601</v>
       </c>
       <c r="B4" t="n">
-        <v>56632</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -946,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>290957.2190817917</v>
+        <v>291034</v>
       </c>
       <c r="R4" t="n">
-        <v>6520363.568089969</v>
+        <v>6520399</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -976,22 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-06-09</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-06-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-16</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1023,37 +1008,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105271387</v>
+        <v>105271603</v>
       </c>
       <c r="B5" t="n">
-        <v>56859</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1072,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>290923.1034794095</v>
+        <v>291101</v>
       </c>
       <c r="R5" t="n">
-        <v>6520368.009731309</v>
+        <v>6520544</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1102,22 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-06-09</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-06-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-16</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1149,37 +1119,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105271618</v>
+        <v>105271387</v>
       </c>
       <c r="B6" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103055</v>
+        <v>103018</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1189,7 +1154,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1198,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>290221.9399532279</v>
+        <v>290924</v>
       </c>
       <c r="R6" t="n">
-        <v>6519696.122596893</v>
+        <v>6520368</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1228,22 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-05-16</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-05-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1272,6 +1227,1560 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>105271388</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mungseröd Vindpark, Boh</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>291003</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6520269</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>JPN0009 (Calluna AB) häckfågelinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>105271473</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mungseröd Vindpark, Boh</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>291084</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6520518</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>JPN0009 (Calluna AB) häckfågelinventering</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>105271474</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mungseröd Vindpark, Boh</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>291099</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6520523</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>JPN0009 (Calluna AB) häckfågelinventering</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>105271718</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mungseröd Vindpark, Boh</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>291299</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6520710</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-04-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-04-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>JPN0009 (Calluna AB) häckfågelinventering</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>89261908</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>200 m N om jaktstuga, Mungseröd, mellan skogsbilväg (V om) och berg, Boh</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>291118</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6520489</v>
+      </c>
+      <c r="S11" t="n">
+        <v>100</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>1999-09-03</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>1999-09-03</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Bohusläns flora - 2011.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Bäckravin, sumpskog, bäck</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Evastina Blomgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kjell Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Bohusläns Flora 2011</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>89261905</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>200 m N om jaktstuga, Mungseröd, mellan skogsbilväg (V om) och berg, Boh</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>291118</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6520489</v>
+      </c>
+      <c r="S12" t="n">
+        <v>100</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>1999-09-03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>1999-09-03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Bohusläns flora - 2011.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Bäckravin, sumpskog, bäck</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Evastina Blomgren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kjell Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Bohusläns Flora 2011</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>89261913</v>
+      </c>
+      <c r="B13" t="n">
+        <v>104253</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222395</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dvärghäxört</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Circaea alpina</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>200 m N om jaktstuga, Mungseröd, mellan skogsbilväg (V om) och berg, Boh</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>291118</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6520489</v>
+      </c>
+      <c r="S13" t="n">
+        <v>100</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>1999-09-03</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>1999-09-03</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Bohusläns flora - 2011. Dvärghäxört angiven i Fries (St. Nn)</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Bäckravin, sumpskog, bäck</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Evastina Blomgren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kjell Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Bohusläns Flora 2011</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>105271446</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mungseröd Vindpark, Boh</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>290856</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6520266</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>JPN0009 (Calluna AB) häckfågelinventering</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>105271447</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mungseröd Vindpark, Boh</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>290837</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6520254</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>JPN0009 (Calluna AB) häckfågelinventering</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>105271600</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mungseröd Vindpark, Boh</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>290840</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6520245</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-05-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-05-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>JPN0009 (Calluna AB) häckfågelinventering</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>105271476</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mungseröd Vindpark, Boh</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>290811</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6520236</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>JPN0009 (Calluna AB) häckfågelinventering</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>105271622</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mungseröd Vindpark, Boh</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>290662</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6520163</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-05-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-05-16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>JPN0009 (Calluna AB) häckfågelinventering</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>105271623</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mungseröd Vindpark, Boh</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>290363</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6519863</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-05-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-05-16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>JPN0009 (Calluna AB) häckfågelinventering</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>105271618</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mungseröd Vindpark, Boh</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>290222</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6519696</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-05-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-05-16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>JPN0009 (Calluna AB) häckfågelinventering</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59265-2024 artfynd.xlsx
+++ b/artfynd/A 59265-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105271470</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105271445</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105271601</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105271603</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105271387</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105271388</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105271473</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,6 +1600,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105271474</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1671,6 +1716,11 @@
           <t>Bohusläns Flora 2011</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89261908</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1782,6 +1832,11 @@
           <t>Bohusläns Flora 2011</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89261905</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1893,6 +1948,11 @@
           <t>Bohusläns Flora 2011</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89261913</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2004,6 +2064,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105271718</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2115,6 +2180,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105271446</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2226,6 +2296,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105271447</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2337,6 +2412,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105271600</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2448,6 +2528,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105271476</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2559,6 +2644,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105271622</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2670,6 +2760,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105271623</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2781,8 +2876,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105271618</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>